--- a/data/trans_dic/IP19C04-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C04-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por extracción de algún diente o muela</t>
+          <t>Menores que en su última visita al dentista fue por extracción de algún diente o muela (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 12,47</t>
+          <t>1,42; 12,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 23,99</t>
+          <t>6,67; 22,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 21,3</t>
+          <t>2,46; 21,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,6</t>
+          <t>0,0; 11,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 21,65</t>
+          <t>4,89; 22,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,9</t>
+          <t>1,39; 12,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,99</t>
+          <t>0,0; 12,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,37</t>
+          <t>0,0; 18,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 13,96</t>
+          <t>4,22; 14,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,97; 15,18</t>
+          <t>5,72; 15,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 11,88</t>
+          <t>1,43; 12,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 11,13</t>
+          <t>0,7; 10,82</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,54</t>
+          <t>3,68; 9,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 9,79</t>
+          <t>4,11; 9,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 8,13</t>
+          <t>3,69; 8,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 8,4</t>
+          <t>3,04; 8,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 9,58</t>
+          <t>4,41; 9,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 10,21</t>
+          <t>4,31; 9,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,28</t>
+          <t>2,78; 7,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,93</t>
+          <t>1,82; 5,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 8,51</t>
+          <t>4,72; 8,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,84</t>
+          <t>4,86; 8,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,85</t>
+          <t>3,63; 6,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,9</t>
+          <t>2,76; 5,79</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 10,97</t>
+          <t>2,01; 11,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,23</t>
+          <t>0,0; 6,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 8,2</t>
+          <t>0,88; 9,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 9,06</t>
+          <t>1,97; 9,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 11,13</t>
+          <t>2,2; 11,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,56</t>
+          <t>0,84; 8,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,24</t>
+          <t>0,84; 7,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,13</t>
+          <t>0,8; 7,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 9,48</t>
+          <t>3,17; 9,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,87</t>
+          <t>0,92; 5,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,11</t>
+          <t>1,24; 6,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,14</t>
+          <t>1,84; 5,75</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,19</t>
+          <t>4,02; 8,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 8,81</t>
+          <t>4,48; 8,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,5</t>
+          <t>3,6; 7,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,17</t>
+          <t>2,89; 7,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 9,5</t>
+          <t>5,28; 9,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,9</t>
+          <t>4,14; 7,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,99</t>
+          <t>2,45; 5,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,03</t>
+          <t>2,04; 4,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,06</t>
+          <t>5,13; 8,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,69</t>
+          <t>4,65; 7,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,05</t>
+          <t>3,47; 6,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,22</t>
+          <t>2,88; 5,21</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por extracción de algún diente o muela (tasa de respuesta: 99,51%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2553</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>7388</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8495</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2626</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1933</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>667; 5782</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3197; 10700</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>558; 4894</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3357</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2099; 9444</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>597; 5342</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3597</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4604</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3791; 12736</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5205; 14161</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>728; 6345</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>387; 5976</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>13934</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14200</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14190</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13268</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16461</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>16214</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11373</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>10825</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>30396</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>30414</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>25563</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>24093</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>8407; 21144</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9064; 21197</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9314; 21109</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7968; 21349</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>10825; 23566</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>10385; 23857</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7036; 18195</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>5884; 17897</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>22381; 38919</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>22409; 41050</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>18351; 33821</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>16134; 33867</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4032</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3091</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4399</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4323</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2774</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3563</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>8354</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4290</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>7962</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1522; 8549</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5225</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>774; 8292</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1975; 9194</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1606; 8714</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>694; 6810</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>734; 6502</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1082; 10046</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4711; 14354</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1538; 8567</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2175; 10875</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4334; 13561</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>20519</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22220</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19181</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18379</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>25619</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20978</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>14445</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>15609</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>46138</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>43199</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>33626</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>33988</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>14119; 28552</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>15861; 31414</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>13070; 26731</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11319; 27500</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>19093; 35073</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>15142; 29179</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>9018; 21743</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>9892; 23604</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>36529; 58819</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>33459; 55034</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>25371; 44038</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>25192; 45601</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C04-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C04-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 12,32</t>
+          <t>1,35; 12,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 22,31</t>
+          <t>7,13; 23,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 21,54</t>
+          <t>2,51; 22,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,29</t>
+          <t>0,0; 10,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 22,02</t>
+          <t>4,95; 21,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 12,44</t>
+          <t>1,44; 12,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,78</t>
+          <t>0,0; 13,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,07</t>
+          <t>0,0; 19,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 14,18</t>
+          <t>4,31; 13,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,72; 15,57</t>
+          <t>5,08; 15,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 12,47</t>
+          <t>1,42; 11,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 10,82</t>
+          <t>0,69; 11,3</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 9,26</t>
+          <t>3,86; 9,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,11; 9,61</t>
+          <t>4,03; 9,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 8,35</t>
+          <t>3,87; 8,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 8,15</t>
+          <t>3,03; 8,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 9,59</t>
+          <t>4,43; 9,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 9,9</t>
+          <t>4,32; 9,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,2</t>
+          <t>2,69; 7,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,54</t>
+          <t>1,87; 5,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,21</t>
+          <t>4,71; 8,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,9</t>
+          <t>4,89; 8,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,69</t>
+          <t>3,52; 6,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,79</t>
+          <t>2,79; 5,77</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 11,3</t>
+          <t>2,32; 10,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,11</t>
+          <t>0,0; 5,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 9,45</t>
+          <t>0,79; 8,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 9,19</t>
+          <t>1,93; 8,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 11,92</t>
+          <t>2,2; 11,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,29</t>
+          <t>0,83; 7,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,41</t>
+          <t>0,84; 7,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,39</t>
+          <t>0,65; 6,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 9,65</t>
+          <t>3,07; 9,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,11</t>
+          <t>0,88; 5,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,2</t>
+          <t>1,44; 6,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,75</t>
+          <t>1,63; 6,08</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,14</t>
+          <t>3,95; 8,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,87</t>
+          <t>4,42; 8,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 7,36</t>
+          <t>3,68; 7,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,02</t>
+          <t>3,14; 6,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 9,7</t>
+          <t>5,1; 9,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,97</t>
+          <t>3,91; 8,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,9</t>
+          <t>2,51; 5,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,87</t>
+          <t>2,0; 4,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 8,25</t>
+          <t>5,0; 7,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,64</t>
+          <t>4,66; 7,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,02</t>
+          <t>3,53; 5,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,21</t>
+          <t>2,77; 5,19</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>667; 5782</t>
+          <t>635; 5924</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3197; 10700</t>
+          <t>3420; 11372</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>558; 4894</t>
+          <t>569; 5164</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3357</t>
+          <t>0; 3222</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2099; 9444</t>
+          <t>2123; 9267</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>597; 5342</t>
+          <t>617; 5447</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3597</t>
+          <t>0; 3919</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4604</t>
+          <t>0; 4985</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3791; 12736</t>
+          <t>3870; 12427</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5205; 14161</t>
+          <t>4621; 14133</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>728; 6345</t>
+          <t>720; 6015</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>387; 5976</t>
+          <t>379; 6237</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8407; 21144</t>
+          <t>8813; 20789</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9064; 21197</t>
+          <t>8883; 21371</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9314; 21109</t>
+          <t>9775; 21535</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7968; 21349</t>
+          <t>7934; 21904</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10825; 23566</t>
+          <t>10895; 23059</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10385; 23857</t>
+          <t>10406; 23639</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7036; 18195</t>
+          <t>6799; 17917</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5884; 17897</t>
+          <t>6043; 18342</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22381; 38919</t>
+          <t>22323; 39719</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22409; 41050</t>
+          <t>22575; 40503</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18351; 33821</t>
+          <t>17775; 33998</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16134; 33867</t>
+          <t>16309; 33769</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1522; 8549</t>
+          <t>1756; 8001</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5225</t>
+          <t>0; 4735</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>774; 8292</t>
+          <t>691; 7481</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1975; 9194</t>
+          <t>1930; 8478</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1606; 8714</t>
+          <t>1607; 8701</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>694; 6810</t>
+          <t>685; 6272</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>734; 6502</t>
+          <t>736; 6270</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1082; 10046</t>
+          <t>889; 8663</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4711; 14354</t>
+          <t>4567; 14078</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1538; 8567</t>
+          <t>1478; 8522</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2175; 10875</t>
+          <t>2526; 10710</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4334; 13561</t>
+          <t>3837; 14352</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14119; 28552</t>
+          <t>13855; 28870</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15861; 31414</t>
+          <t>15659; 31640</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13070; 26731</t>
+          <t>13357; 27656</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11319; 27500</t>
+          <t>12298; 27037</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19093; 35073</t>
+          <t>18465; 34049</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15142; 29179</t>
+          <t>14294; 29573</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9018; 21743</t>
+          <t>9254; 21615</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9892; 23604</t>
+          <t>9669; 23862</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36529; 58819</t>
+          <t>35600; 56580</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33459; 55034</t>
+          <t>33571; 54266</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25371; 44038</t>
+          <t>25839; 43764</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25192; 45601</t>
+          <t>24239; 45443</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C04-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C04-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,27%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>13,56%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8,36%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,27%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 12,62</t>
+          <t>5,24; 21,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,13; 23,71</t>
+          <t>1,4; 12,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 22,73</t>
+          <t>0,0; 12,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,84</t>
+          <t>0,0; 22,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 21,61</t>
+          <t>1,38; 12,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,68</t>
+          <t>6,94; 23,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,93</t>
+          <t>2,48; 21,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,56</t>
+          <t>0,0; 13,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 13,84</t>
+          <t>4,61; 13,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 15,54</t>
+          <t>4,97; 15,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 11,83</t>
+          <t>1,42; 11,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 11,3</t>
+          <t>0,5; 11,58</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,1%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>6,44%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,61%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,73%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 9,11</t>
+          <t>4,4; 9,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 9,69</t>
+          <t>4,38; 10,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 8,52</t>
+          <t>2,65; 7,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 8,37</t>
+          <t>1,79; 5,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 9,38</t>
+          <t>3,98; 9,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 9,81</t>
+          <t>4,09; 9,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,09</t>
+          <t>3,41; 8,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,68</t>
+          <t>2,78; 7,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,38</t>
+          <t>4,73; 8,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 8,78</t>
+          <t>4,84; 8,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,73</t>
+          <t>3,61; 6,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,77</t>
+          <t>2,7; 5,4</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,33%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,77%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,52%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 10,57</t>
+          <t>2,01; 11,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,53</t>
+          <t>0,83; 7,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 8,53</t>
+          <t>0,85; 7,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 8,47</t>
+          <t>0,73; 6,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 11,9</t>
+          <t>1,86; 10,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,64</t>
+          <t>0,0; 6,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,15</t>
+          <t>1,03; 8,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,37</t>
+          <t>1,81; 8,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 9,46</t>
+          <t>3,03; 9,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,08</t>
+          <t>1,13; 4,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,1</t>
+          <t>1,25; 6,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,08</t>
+          <t>1,81; 6,15</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,85%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,28%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,28%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,23</t>
+          <t>5,24; 9,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,94</t>
+          <t>3,98; 7,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,61</t>
+          <t>2,4; 5,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,9</t>
+          <t>1,93; 4,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,41</t>
+          <t>4,11; 8,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,08</t>
+          <t>4,5; 8,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,86</t>
+          <t>3,59; 7,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,93</t>
+          <t>2,91; 6,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,94</t>
+          <t>5,12; 8,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,54</t>
+          <t>4,6; 7,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 5,98</t>
+          <t>3,41; 6,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,19</t>
+          <t>2,65; 5,01</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2553</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>6504</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1900</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4835</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>673</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1819</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>635; 5924</t>
+          <t>2249; 9288</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3420; 11372</t>
+          <t>603; 5541</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>569; 5164</t>
+          <t>0; 3655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3222</t>
+          <t>0; 5383</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2123; 9267</t>
+          <t>648; 5852</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>617; 5447</t>
+          <t>3328; 11507</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3919</t>
+          <t>564; 4840</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4985</t>
+          <t>0; 3714</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3870; 12427</t>
+          <t>4143; 12536</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4621; 14133</t>
+          <t>4521; 13805</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>720; 6015</t>
+          <t>723; 6043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>379; 6237</t>
+          <t>257; 5899</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16461</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16214</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11373</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9862</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>13934</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14200</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>14190</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13268</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16461</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16214</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11373</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24093</t>
+          <t>22054</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8813; 20789</t>
+          <t>10823; 23528</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8883; 21371</t>
+          <t>10545; 24606</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9775; 21535</t>
+          <t>6692; 18394</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7934; 21904</t>
+          <t>5541; 17287</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10895; 23059</t>
+          <t>9082; 21791</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10406; 23639</t>
+          <t>9016; 21575</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6799; 17917</t>
+          <t>8606; 20540</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6043; 18342</t>
+          <t>7404; 19285</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22323; 39719</t>
+          <t>22402; 40344</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22575; 40503</t>
+          <t>22351; 40791</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17775; 33998</t>
+          <t>18266; 34618</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16309; 33769</t>
+          <t>15526; 31110</t>
         </is>
       </c>
     </row>
@@ -1789,37 +1789,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4323</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2774</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3426</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4032</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1516</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3091</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4399</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4323</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2774</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>7785</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1756; 8001</t>
+          <t>1469; 8136</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4735</t>
+          <t>679; 6212</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>691; 7481</t>
+          <t>744; 6347</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1930; 8478</t>
+          <t>923; 7929</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1607; 8701</t>
+          <t>1408; 8306</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>685; 6272</t>
+          <t>0; 5330</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>736; 6270</t>
+          <t>899; 7196</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>889; 8663</t>
+          <t>1873; 8984</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4567; 14078</t>
+          <t>4514; 14100</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1478; 8522</t>
+          <t>1898; 8161</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2526; 10710</t>
+          <t>2197; 10725</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3837; 14352</t>
+          <t>4179; 14189</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>25619</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20978</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14445</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14433</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>20519</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>22220</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>19181</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18379</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>25619</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20978</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14445</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33988</t>
+          <t>31657</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13855; 28870</t>
+          <t>18948; 34357</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15659; 31640</t>
+          <t>14563; 28916</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13357; 27656</t>
+          <t>8866; 22080</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12298; 27037</t>
+          <t>8914; 22960</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18465; 34049</t>
+          <t>14407; 28733</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14294; 29573</t>
+          <t>15946; 31191</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9254; 21615</t>
+          <t>13055; 27246</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9669; 23862</t>
+          <t>11527; 25018</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35600; 56580</t>
+          <t>36483; 57423</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33571; 54266</t>
+          <t>33116; 55403</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25839; 43764</t>
+          <t>24962; 44272</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24239; 45443</t>
+          <t>22739; 42952</t>
         </is>
       </c>
     </row>
